--- a/aimagine/from-scratch/series_log.xlsx
+++ b/aimagine/from-scratch/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,226 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep02/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-01 15:42</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1.575</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1c5de02b0f8b0590e9a631fc9272708e_1785598645.mp4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-01 15:45</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8cb10e5ad5ad6cb42ae3d9dafb04b85e_1785599045.mp4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-01 15:47</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0eab57d074599980d1d168c4670559d8_1785599204.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-01 15:49</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/85f5ed0128edcd2dff94ae0cd68597c6_1785599341.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep03/shots/shot_04.mp4</t>
         </is>
       </c>
     </row>

--- a/aimagine/from-scratch/series_log.xlsx
+++ b/aimagine/from-scratch/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,6 +927,226 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-02 15:43</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1.575</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/effe1466c87d789cb8f76b520f4723ff_1785685141.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-02 15:47</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e28db95d86622296ae07560dae8e91e1_1785685599.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-02 15:49</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c988cb996126be07f9d242f687a38195_1785685736.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-02 15:52</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cbee955dba967406c8c1038f86259ada_1785685879.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/from-scratch/series_log.xlsx
+++ b/aimagine/from-scratch/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,226 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-03 17:02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/681df791c13f9db4fb999217a01308cd_1785776354.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-03 17:05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3e6a9d8e59ce61c7be8672e347bff2ed_1785776711.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-03 17:10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/34b54aea2d88fe31e9994411c417dbfa_1785776869.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-03 17:12</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/87edc1fb19ebfb8390b63cf34cbb250d_1785777154.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep05/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/from-scratch/series_log.xlsx
+++ b/aimagine/from-scratch/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,6 +1367,1326 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-07 18:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>378.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9afd756b87984af91b5ce9a2f7d99a8f_1786125319.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-08 15:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4593c9a1c0bfc0457b0e84ab075f0e48_1786201182.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-08 15:05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/312acf735b2540cc3db59c30e9dab94f_1786201372.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-08 15:11</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cc181e5e51472a839dd0ca1b7a7dbc62_1786201642.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-08 15:15</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/82e7fafeb681cdde26f1b90f39e9a1cf_1786201959.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-08 15:19</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a887a0444ce67c91e4abac5c403377bf_1786202203.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:42</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/682f90b14ea879dd4899bd1acaf93f63_1786221654.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:45</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e785d8587fd8b959b4a6b4cb9f2b04be_1786221867.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:48</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/727e44866bd3dc7f6b4e4790583ff4ae_1786222033.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:53</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/046eeca4caa06748a0573d2f6ddfe30f_1786222204.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:56</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/09b43fec196aed7b18dc873c24cab7dc_1786222502.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:58</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9d4b3ed58965da28d4a60a452340946d_1786222683.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:15</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/638630fbfc5f4a49f2004f81049b47fb_1786223509.mp4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:17</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5713707d99bc64dbc4fb9b6a3c68e405_1786223787.mp4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:23</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/da29f56fcf0778f1a94b9e75ae770ac6_1786223964.mp4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:27</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/89399f342a417f0a73ab8a440e18704f_1786224286.mp4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:30</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ee313239cca145294a1ca7b4bf663ed2_1786224535.mp4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-08 21:33</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/605ead144d508c7b390f0fa70781f587_1786224726.mp4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-08 22:19</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8ffb8af0fb7282516648e9238cb8f899_1786227398.mp4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-08 22:21</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d7c9cd3b1e348530f696fe2427e7551a_1786227660.mp4</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-08 22:24</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/025d401b4797e849d23f0d851647d8b0_1786227811.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-08 22:27</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0a1da5d60d9b9db7cb225e0c443c67ce_1786228009.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-08 22:30</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a60b7b0ceefbddcc5d30c9a4d29cc881_1786228184.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-08 22:34</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/27c925e3ffa59ffb290db339320c7c13_1786228344.mp4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep06/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/from-scratch/series_log.xlsx
+++ b/aimagine/from-scratch/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2687,6 +2687,862 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-09 15:06</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/554bbe68e4c9af252fa3371292755666_1786287804.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-09 15:11</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/adc4d47a56bca6aeeafe75323c75a94e_1786288129.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-09 15:16</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/816cb8b3aee94defe10c87018db28da0_1786288403.mp4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-09 15:20</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/db2f473bbecbdb5e239e210b75b1dce4_1786288675.mp4</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-09 15:22</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2d3c1b9acbbbaeecb3247915f67dfaa0_1786288937.mp4</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-13 15:52</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a6af30d066ddd16746d047a8cc8bd2de_1786635295.mp4</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-13 16:24</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/27bbaeedf8e654389cc24e2ecafb623b_1786636595.mp4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-13 16:31</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/09f4bc8fbf14c167d74317873a12f7f2_1786638427.mp4</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-13 16:50</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/25cc872d7cb2bc70a78871a1d14fd1fa_1786638999.mp4</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-13 16:53</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/32cfc86d361d86a8687b8260afd9e25a_1786639972.mp4</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:27</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:32</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:43</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c2d982ac949c62e15cefa437b8edcc98_1786721921.mp4</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/216a9684d02670116583e774c698e47b_1786722483.mp4</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2e108bead846ec69513c4982f740ee88_1786723135.mp4</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:08</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d7edd4bf4079a71aeed2867106b577d4_1786723664.mp4</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep07/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/from-scratch/series_log.xlsx
+++ b/aimagine/from-scratch/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3543,6 +3543,2103 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-15 14:52</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/aebda33768c35a06b85679bcb2c6714d_1786805394.mp4</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-15 14:55</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0060424adb18f033371c5f94b50f4439_1786805668.mp4</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:00</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/779ee3be61f01f2cb97654bc56cddae8_1786805824.mp4</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:02</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/dfdf42ac51196771a21242050dbf18c3_1786806108.mp4</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:07</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/88dd472f708cf7b31d11846020161585_1786806263.mp4</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:08</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5e07119eb690fad825fbe76c845c98af_1786806513.mp4</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-16 14:52</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/86ae82f4fa3e0ce324e5b293413d0ead_1786891790.mp4</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-16 14:57</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/717b514f8ccbd3a2452cd10c501192a4_1786892058.mp4</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-16 15:06</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f0d15427fd55e95e83e8a9eb958b3206_1786892441.mp4</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-16 15:10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1eaa46f23a803e6536e21af176e0ca57_1786892879.mp4</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-16 15:13</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/afb0d93be6eb5e2e38823b2bc349816a_1786893167.mp4</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-17 14:59</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8b13a8be33590b478518cc6966b944e3_1786978562.mp4</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:05</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b6368e5796c2d378c959ff094101d93f_1786978860.mp4</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fbfa811890180cb183377e3a763f1c76_1786979227.mp4</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:15</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/dc279704fd21be7680a3489e12308139_1786979553.mp4</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:18</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4535bd524248447a6ba731d0c81fb642_1786979894.mp4</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:06</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b30a005f26a38b79b7a6d33fc7981ad1_1787065428.mp4</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:08</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/34f48f38f2a2c45192b4bd68fa06bf74_1787065674.mp4</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:11</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/93b065adcb88a1cd5e8015ea499f7beb_1787065848.mp4</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:16</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/79747ffa0c80528ce51eaf6f54acf6f6_1787065982.mp4</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:18</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3aa72c21265829e587a93c03224df913_1787066252.mp4</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:22</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a4d83ebf91ce238ec042d6862e00cd22_1787066400.mp4</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-19 15:06</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c82a02e30d8d95c0780d398e6a68105f_1787151799.mp4</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-19 15:14</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2009492a1651be559d5fc4486e7068fa_1787152228.mp4</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-19 15:23</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cb00c7af1731c015db4d09d514c0f99a_1787152558.mp4</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-19 15:34</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b3c136d5b3449744324664e3f90c53d4_1787153438.mp4</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-19 15:46</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/13b2f6e800678efe3e526234405604f0_1787153810.mp4</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:09</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:19</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5e23a5c3cbbd3a1ccddf49735a0d0cc4_1787238677.mp4</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:28</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ebf7e56873356dff7735a47bed5bb632_1787239419.mp4</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:32</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:37</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:41</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:06</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/85a187690108ec36509497b21d7271cf_1787324732.mp4</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:13</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e2d0647bcb32e0b581f0e13bd382989c_1787324918.mp4</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:15</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ed65b255a5c7265b6f3ac7caf4ddf812_1787325303.mp4</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:18</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/53e9309115c825c79b5804337bbcb9e6_1787325490.mp4</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:25</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d986f69f60f7c3145d9c9b26fefcb991_1787325715.mp4</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:29</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e6fad7083eb4aad94cf211fa8680fcec_1787326008.mp4</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep08/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/from-scratch/series_log.xlsx
+++ b/aimagine/from-scratch/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:M108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5640,6 +5640,666 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-22 15:07</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6824ee45b6d3e496676f38268e5c2f65_1787410166.mp4</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep09/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:19</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cd24197cfa3c5de45990b3ed88e1ee7c_1787670963.mp4</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep09/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:34</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3a954d1b6931a20ad737ba5796fcd3fd_1787671879.mp4</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep09/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:38</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8529ad6196d5212c0e6a9274cc150baa_1787672148.mp4</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep09/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:40</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8717e93b454d5855f9b16f72bdd6eb9c_1787672389.mp4</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep09/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-25 15:45</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d7602e4139a8a6bb867bc88173d50782_1787672581.mp4</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep09/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:09</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/56baad77fe350217d5d4af7056296997_1787760058.mp4</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep09/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:13</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7c3932f539760a299fada6295cba6d52_1787760744.mp4</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep09/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:30</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/386f66be99ea8a271bbd290d0ff65e36_1787760911.mp4</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep09/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:33</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c0a2e5777f58f444546a882edc083633_1787761905.mp4</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep09/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:41</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6f0296153e54c7de827345885c200eb1_1787762141.mp4</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep09/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:44</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2429b47e51ddd5ac897eeca05290c20d_1787762589.mp4</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep09/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/from-scratch/series_log.xlsx
+++ b/aimagine/from-scratch/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M108"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6300,6 +6300,336 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:57</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8d9dcc47c7a3eaf2bc58bb867289190d_1787874979.mp4</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:59</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/30c786555cd15dc18b2932253fe2c469_1787875128.mp4</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep10/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-28 00:05</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f546ad27c0cc3a1f6b4cc39fc818a206_1787875283.mp4</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep10/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-28 00:07</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2d035a2739350f4e45635c097d3e959a_1787875625.mp4</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep10/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-28 00:13</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/94123755a74c63a61a0004138fd424c3_1787875847.mp4</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep10/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-28 00:16</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3347b17ea2e6e962c3d41a10fe8e23a5_1787876132.mp4</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/from-scratch/episodes/ep10/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
